--- a/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_RIGALLI-ALGINET.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_RIGALLI-ALGINET.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X13"/>
+  <dimension ref="A1:X14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>J. DALMAU ROIG</t>
+          <t>L. VERDEGUER FERRER</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -562,76 +562,76 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>6.7134</v>
+        <v>11.9012</v>
       </c>
       <c r="E2" t="n">
-        <v>6.113</v>
+        <v>11.5795</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6002999999999998</v>
+        <v>0.3217000000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.8089999999999999</v>
+        <v>6.2685</v>
       </c>
       <c r="H2" t="n">
-        <v>-2.6731</v>
+        <v>4.3896</v>
       </c>
       <c r="I2" t="n">
-        <v>1.8641</v>
+        <v>1.879</v>
       </c>
       <c r="J2" t="n">
-        <v>2.5928</v>
+        <v>10.285</v>
       </c>
       <c r="K2" t="n">
-        <v>-1.7722</v>
+        <v>7.4642</v>
       </c>
       <c r="L2" t="n">
-        <v>4.365</v>
+        <v>2.8207</v>
       </c>
       <c r="M2" t="n">
-        <v>-3.4018</v>
+        <v>-4.0166</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.9007999999999999</v>
+        <v>-3.0746</v>
       </c>
       <c r="O2" t="n">
-        <v>-2.501</v>
+        <v>-0.9417000000000002</v>
       </c>
       <c r="P2" t="n">
-        <v>3.601</v>
+        <v>4.8684</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.2001</v>
+        <v>-4.2842</v>
       </c>
       <c r="R2" t="n">
-        <v>3.8011</v>
+        <v>9.152699999999999</v>
       </c>
       <c r="S2" t="n">
-        <v>2.6526</v>
+        <v>5.4645</v>
       </c>
       <c r="T2" t="n">
-        <v>1.3207</v>
+        <v>4.6157</v>
       </c>
       <c r="U2" t="n">
-        <v>1.3319</v>
+        <v>0.8487999999999998</v>
       </c>
       <c r="V2" t="n">
-        <v>1.2687</v>
+        <v>-4.700299999999999</v>
       </c>
       <c r="W2" t="n">
-        <v>2.3996</v>
+        <v>0.9632000000000001</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.1308</v>
+        <v>-5.6635</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. BOSCH ROIG</t>
+          <t>J. MARTIN FERNANDEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>3.7349</v>
+        <v>6.9258</v>
       </c>
       <c r="E3" t="n">
-        <v>1.5143</v>
+        <v>16.0741</v>
       </c>
       <c r="F3" t="n">
-        <v>2.2207</v>
+        <v>-9.148399999999999</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.04760000000000009</v>
+        <v>6.7826</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2548</v>
+        <v>6.5372</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3024</v>
+        <v>0.2454999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5983999999999998</v>
+        <v>11.5518</v>
       </c>
       <c r="K3" t="n">
-        <v>0.5488999999999999</v>
+        <v>9.2013</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0495000000000001</v>
+        <v>2.3505</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.6459999999999999</v>
+        <v>-4.7692</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.2941</v>
+        <v>-2.6642</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.3519</v>
+        <v>-2.105</v>
       </c>
       <c r="P3" t="n">
-        <v>1.6005</v>
+        <v>1.9472</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.2004</v>
+        <v>-5.8421</v>
       </c>
       <c r="R3" t="n">
-        <v>2.8008</v>
+        <v>7.789400000000001</v>
       </c>
       <c r="S3" t="n">
-        <v>3.3819</v>
+        <v>9.6928</v>
       </c>
       <c r="T3" t="n">
-        <v>1.8564</v>
+        <v>9.9603</v>
       </c>
       <c r="U3" t="n">
-        <v>1.5254</v>
+        <v>-0.2675000000000001</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.1998</v>
+        <v>-11.4969</v>
       </c>
       <c r="W3" t="n">
-        <v>0.2598</v>
+        <v>0.4042000000000001</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.4596</v>
+        <v>-11.9009</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. ZURBRIGGEN</t>
+          <t>J. DALMAU ROIG</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>2.813</v>
+        <v>1.279299999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.7364000000000002</v>
+        <v>4.3268</v>
       </c>
       <c r="F4" t="n">
-        <v>3.5494</v>
+        <v>-3.0473</v>
       </c>
       <c r="G4" t="n">
-        <v>-2.9763</v>
+        <v>-8.1607</v>
       </c>
       <c r="H4" t="n">
-        <v>-2.0271</v>
+        <v>-9.4808</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.9492</v>
+        <v>1.3201</v>
       </c>
       <c r="J4" t="n">
-        <v>-2.0155</v>
+        <v>2.2731</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.7471</v>
+        <v>-4.1482</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.2684</v>
+        <v>6.4211</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.9606999999999999</v>
+        <v>-10.4337</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.28</v>
+        <v>-5.3327</v>
       </c>
       <c r="O4" t="n">
-        <v>0.3192</v>
+        <v>-5.101100000000001</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.6002000000000001</v>
+        <v>8.957800000000001</v>
       </c>
       <c r="Q4" t="n">
-        <v>-4.4013</v>
+        <v>-4.2842</v>
       </c>
       <c r="R4" t="n">
-        <v>3.8011</v>
+        <v>13.242</v>
       </c>
       <c r="S4" t="n">
-        <v>0.9026999999999999</v>
+        <v>1.6439</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.7577</v>
+        <v>1.4538</v>
       </c>
       <c r="U4" t="n">
-        <v>1.6604</v>
+        <v>0.1903</v>
       </c>
       <c r="V4" t="n">
-        <v>5.486800000000001</v>
+        <v>-1.1618</v>
       </c>
       <c r="W4" t="n">
-        <v>6.438099999999999</v>
+        <v>4.8844</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.9513</v>
+        <v>-6.0461</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. MARTIN FERNANDEZ</t>
+          <t>M. MARTINEZ HERNANDEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>2.7088</v>
+        <v>0.7976999999999994</v>
       </c>
       <c r="E5" t="n">
-        <v>7.6919</v>
+        <v>-2.4775</v>
       </c>
       <c r="F5" t="n">
-        <v>-4.9831</v>
+        <v>3.2752</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7802</v>
+        <v>-0.3994999999999997</v>
       </c>
       <c r="H5" t="n">
-        <v>2.1594</v>
+        <v>0.3553999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.3792</v>
+        <v>-0.7549000000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>4.5243</v>
+        <v>4.3575</v>
       </c>
       <c r="K5" t="n">
-        <v>3.1245</v>
+        <v>3.3078</v>
       </c>
       <c r="L5" t="n">
-        <v>1.3998</v>
+        <v>1.0498</v>
       </c>
       <c r="M5" t="n">
-        <v>-3.7442</v>
+        <v>-4.7569</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.9651</v>
+        <v>-2.9522</v>
       </c>
       <c r="O5" t="n">
-        <v>-2.779</v>
+        <v>-1.8048</v>
       </c>
       <c r="P5" t="n">
-        <v>1.0003</v>
+        <v>3.7</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.0003</v>
+        <v>-9.1526</v>
       </c>
       <c r="R5" t="n">
-        <v>2.0005</v>
+        <v>12.8525</v>
       </c>
       <c r="S5" t="n">
-        <v>4.4473</v>
+        <v>-3.8021</v>
       </c>
       <c r="T5" t="n">
-        <v>3.9081</v>
+        <v>-2.8461</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5392</v>
+        <v>-0.9559</v>
       </c>
       <c r="V5" t="n">
-        <v>-3.519</v>
+        <v>1.2992</v>
       </c>
       <c r="W5" t="n">
-        <v>0.2598</v>
+        <v>5.1638</v>
       </c>
       <c r="X5" t="n">
-        <v>-3.7788</v>
+        <v>-3.8644</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. MARTINEZ HERNANDEZ</t>
+          <t>M. CHOJNACKI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>2.4413</v>
+        <v>-0.2005000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3210999999999999</v>
+        <v>0.8925999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>2.1202</v>
+        <v>-1.0932</v>
       </c>
       <c r="G6" t="n">
-        <v>1.5982</v>
+        <v>-0.256</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4453</v>
+        <v>0.1427</v>
       </c>
       <c r="I6" t="n">
-        <v>2.0435</v>
+        <v>-0.3987</v>
       </c>
       <c r="J6" t="n">
-        <v>3.4164</v>
+        <v>0.0334</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6416000000000001</v>
+        <v>0.6979</v>
       </c>
       <c r="L6" t="n">
-        <v>2.7748</v>
+        <v>-0.6645</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.8183</v>
+        <v>-0.2895</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.0869</v>
+        <v>-0.5553</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.7314000000000001</v>
+        <v>0.2658</v>
       </c>
       <c r="P6" t="n">
-        <v>1.2003</v>
+        <v>-0.1948</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3.401</v>
+        <v>-0.9737</v>
       </c>
       <c r="R6" t="n">
-        <v>4.6013</v>
+        <v>0.7789</v>
       </c>
       <c r="S6" t="n">
-        <v>-2.0652</v>
+        <v>0.2503</v>
       </c>
       <c r="T6" t="n">
-        <v>-2.6938</v>
+        <v>0.6118999999999999</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6286</v>
+        <v>-0.3616</v>
       </c>
       <c r="V6" t="n">
-        <v>1.7081</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>2.9995</v>
+        <v>1.2211</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.2914</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>L. VERDEGUER FERRER</t>
+          <t>P. SILLA TEBAR</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>1.6648</v>
+        <v>-3.418099999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.06400000000000006</v>
+        <v>-2.8152</v>
       </c>
       <c r="F7" t="n">
-        <v>1.7288</v>
+        <v>-0.6031000000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1901000000000002</v>
+        <v>1.043099999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.6751</v>
+        <v>4.6194</v>
       </c>
       <c r="I7" t="n">
-        <v>1.8653</v>
+        <v>-3.5764</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.6924999999999999</v>
+        <v>6.3804</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.3744999999999999</v>
+        <v>6.1585</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.318</v>
+        <v>0.2219000000000007</v>
       </c>
       <c r="M7" t="n">
-        <v>0.8826000000000001</v>
+        <v>-5.3373</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.3006</v>
+        <v>-1.539</v>
       </c>
       <c r="O7" t="n">
-        <v>2.1834</v>
+        <v>-3.7983</v>
       </c>
       <c r="P7" t="n">
-        <v>1.0003</v>
+        <v>-4.6736</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.2004</v>
+        <v>-14.9947</v>
       </c>
       <c r="R7" t="n">
-        <v>2.2007</v>
+        <v>10.3209</v>
       </c>
       <c r="S7" t="n">
-        <v>1.8461</v>
+        <v>-5.1868</v>
       </c>
       <c r="T7" t="n">
-        <v>1.0495</v>
+        <v>-3.866</v>
       </c>
       <c r="U7" t="n">
-        <v>0.7967000000000001</v>
+        <v>-1.3208</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.3717</v>
+        <v>5.399299999999999</v>
       </c>
       <c r="W7" t="n">
-        <v>0.7793999999999999</v>
+        <v>9.6654</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.151</v>
+        <v>-4.2661</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>H. MARTORELL TRONCHONI</t>
+          <t>M. RODILLA ALCAIDE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.9086</v>
+        <v>-3.5486</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1738999999999999</v>
+        <v>-1.748</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.7347</v>
+        <v>-1.8008</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1693</v>
+        <v>-1.1252</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5224000000000001</v>
+        <v>-0.7063</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.353</v>
+        <v>-0.419</v>
       </c>
       <c r="J8" t="n">
-        <v>1.0197</v>
+        <v>5.8363</v>
       </c>
       <c r="K8" t="n">
-        <v>0.9797</v>
+        <v>4.0106</v>
       </c>
       <c r="L8" t="n">
-        <v>0.04</v>
+        <v>1.8256</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.8504</v>
+        <v>-6.9615</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.4573</v>
+        <v>-4.7168</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.393</v>
+        <v>-2.2445</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.4001</v>
+        <v>-0.7789999999999999</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.0003</v>
+        <v>-11.0999</v>
       </c>
       <c r="R8" t="n">
-        <v>0.6002000000000001</v>
+        <v>10.321</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6778</v>
+        <v>-4.1882</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1934</v>
+        <v>-2.4864</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4844000000000001</v>
+        <v>-1.7019</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>2.5436</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>6.0021</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-3.4585</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R. MALLIK BOUNAD</t>
+          <t>V. PELUFO LOZANO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.7441</v>
+        <v>-4.4133</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.918</v>
+        <v>2.369</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.8260000000000001</v>
+        <v>-6.782399999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4533</v>
+        <v>2.3954</v>
       </c>
       <c r="H9" t="n">
-        <v>3.5477</v>
+        <v>4.379300000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-3.0944</v>
+        <v>-1.984</v>
       </c>
       <c r="J9" t="n">
-        <v>2.9195</v>
+        <v>10.4986</v>
       </c>
       <c r="K9" t="n">
-        <v>4.984</v>
+        <v>8.431699999999999</v>
       </c>
       <c r="L9" t="n">
-        <v>-2.0645</v>
+        <v>2.0668</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.4662</v>
+        <v>-8.103299999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.4363</v>
+        <v>-4.0523</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.03</v>
+        <v>-4.0509</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.8002</v>
+        <v>-1.7527</v>
       </c>
       <c r="Q9" t="n">
-        <v>-4.0012</v>
+        <v>-12.8527</v>
       </c>
       <c r="R9" t="n">
-        <v>3.2009</v>
+        <v>11.0999</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.8964000000000001</v>
+        <v>2.8808</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1446</v>
+        <v>3.4288</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.0411</v>
+        <v>-0.5480000000000002</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.5007</v>
+        <v>-7.9367</v>
       </c>
       <c r="W9" t="n">
-        <v>0.0189</v>
+        <v>1.2943</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.5196</v>
+        <v>-9.231</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. RODILLA ALCAIDE</t>
+          <t>A. ZURBRIGGEN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.8856</v>
+        <v>-4.5094</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.2243</v>
+        <v>-15.4795</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.6611</v>
+        <v>10.9701</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.3264</v>
+        <v>-9.3126</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.4123</v>
+        <v>-6.2238</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.9140999999999999</v>
+        <v>-3.0888</v>
       </c>
       <c r="J10" t="n">
-        <v>1.411</v>
+        <v>-7.4846</v>
       </c>
       <c r="K10" t="n">
-        <v>0.8815999999999999</v>
+        <v>-3.7426</v>
       </c>
       <c r="L10" t="n">
-        <v>0.5294</v>
+        <v>-3.742</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.7374</v>
+        <v>-1.828</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.2937</v>
+        <v>-2.4812</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.4436</v>
+        <v>0.6531</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.4004</v>
+        <v>0.3894999999999998</v>
       </c>
       <c r="Q10" t="n">
-        <v>-4.2012</v>
+        <v>-12.0737</v>
       </c>
       <c r="R10" t="n">
-        <v>2.8008</v>
+        <v>12.4631</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.8781</v>
+        <v>-0.3983</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7534</v>
+        <v>-2.3793</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.1246</v>
+        <v>1.9809</v>
       </c>
       <c r="V10" t="n">
-        <v>1.7194</v>
+        <v>4.812</v>
       </c>
       <c r="W10" t="n">
-        <v>2.3192</v>
+        <v>6.458</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.5999</v>
+        <v>-1.6459</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>V. PELUFO LOZANO</t>
+          <t>J. BOSCH ROIG</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.1097</v>
+        <v>-5.1172</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.6265</v>
+        <v>-0.1639000000000002</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.4833</v>
+        <v>-4.953200000000001</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.6179</v>
+        <v>-6.2799</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.9707</v>
+        <v>-1.2695</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.6473</v>
+        <v>-5.0104</v>
       </c>
       <c r="J11" t="n">
-        <v>0.03439999999999999</v>
+        <v>-1.3396</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.2054</v>
+        <v>0.8880000000000001</v>
       </c>
       <c r="L11" t="n">
-        <v>0.24</v>
+        <v>-2.2277</v>
       </c>
       <c r="M11" t="n">
-        <v>-3.6524</v>
+        <v>-4.940300000000001</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.7652</v>
+        <v>-2.1576</v>
       </c>
       <c r="O11" t="n">
-        <v>-2.8872</v>
+        <v>-2.7827</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.4007</v>
+        <v>1.9474</v>
       </c>
       <c r="Q11" t="n">
-        <v>-6.2018</v>
+        <v>-4.2842</v>
       </c>
       <c r="R11" t="n">
-        <v>3.8011</v>
+        <v>6.2315</v>
       </c>
       <c r="S11" t="n">
-        <v>2.2281</v>
+        <v>6.2622</v>
       </c>
       <c r="T11" t="n">
-        <v>2.3411</v>
+        <v>3.6799</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.113</v>
+        <v>2.5825</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.3193</v>
+        <v>-7.0469</v>
       </c>
       <c r="W11" t="n">
-        <v>1.1998</v>
+        <v>1.78</v>
       </c>
       <c r="X11" t="n">
-        <v>-3.5191</v>
+        <v>-8.827</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>P. SILLA TEBAR</t>
+          <t>H. MARTORELL TRONCHONI</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,148 +1342,226 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.7927</v>
+        <v>-6.501600000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.5036</v>
+        <v>-4.8725</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.2892</v>
+        <v>-1.6291</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.2282</v>
+        <v>-3.9218</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.3494</v>
+        <v>-3.0932</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.8788</v>
+        <v>-0.8284</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.1319999999999997</v>
+        <v>-1.8256</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1308</v>
+        <v>-1.2828</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.2627999999999999</v>
+        <v>-0.5428999999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>-3.0962</v>
+        <v>-2.096</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.4802</v>
+        <v>-1.8106</v>
       </c>
       <c r="O12" t="n">
-        <v>-2.616</v>
+        <v>-0.2856</v>
       </c>
       <c r="P12" t="n">
-        <v>-3.8011</v>
+        <v>-2.5316</v>
       </c>
       <c r="Q12" t="n">
-        <v>-6.201700000000001</v>
+        <v>-3.8947</v>
       </c>
       <c r="R12" t="n">
-        <v>2.4006</v>
+        <v>1.3631</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.8715999999999999</v>
+        <v>-0.3276</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.8291</v>
+        <v>0.5685</v>
       </c>
       <c r="U12" t="n">
-        <v>0.9574999999999999</v>
+        <v>-0.8964</v>
       </c>
       <c r="V12" t="n">
-        <v>1.1082</v>
+        <v>0.2795</v>
       </c>
       <c r="W12" t="n">
-        <v>2.6594</v>
+        <v>0.2795</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.5512</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>R. MALLIK BOUNAD</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>RIGALLI-ALGINET</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>6</v>
+      </c>
+      <c r="D13" t="n">
+        <v>-6.5548</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-5.458</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-1.0968</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-3.9631</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.4281</v>
+      </c>
+      <c r="I13" t="n">
+        <v>-5.3912</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3.8469</v>
+      </c>
+      <c r="K13" t="n">
+        <v>5.239599999999999</v>
+      </c>
+      <c r="L13" t="n">
+        <v>-1.3926</v>
+      </c>
+      <c r="M13" t="n">
+        <v>-7.8101</v>
+      </c>
+      <c r="N13" t="n">
+        <v>-3.8115</v>
+      </c>
+      <c r="O13" t="n">
+        <v>-3.9985</v>
+      </c>
+      <c r="P13" t="n">
+        <v>-2.142</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>-12.6578</v>
+      </c>
+      <c r="R13" t="n">
+        <v>10.5158</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.2097</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.4929</v>
+      </c>
+      <c r="U13" t="n">
+        <v>-2.2831</v>
+      </c>
+      <c r="V13" t="n">
+        <v>-0.6595</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0.8601000000000001</v>
+      </c>
+      <c r="X13" t="n">
+        <v>-1.5196</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>--- TOTAL ---</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>RIGALLI-ALGINET</t>
         </is>
       </c>
-      <c r="C13" t="n">
-        <v>2</v>
-      </c>
-      <c r="D13" t="n">
-        <v>1.6355</v>
-      </c>
-      <c r="E13" t="n">
-        <v>4.393600000000001</v>
-      </c>
-      <c r="F13" t="n">
-        <v>-2.758</v>
-      </c>
-      <c r="G13" t="n">
-        <v>-8.814299999999999</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-2.0687</v>
-      </c>
-      <c r="I13" t="n">
-        <v>-6.7455</v>
-      </c>
-      <c r="J13" t="n">
-        <v>13.6765</v>
-      </c>
-      <c r="K13" t="n">
-        <v>8.1919</v>
-      </c>
-      <c r="L13" t="n">
-        <v>5.4848</v>
-      </c>
-      <c r="M13" t="n">
-        <v>-22.491</v>
-      </c>
-      <c r="N13" t="n">
-        <v>-10.2602</v>
-      </c>
-      <c r="O13" t="n">
-        <v>-12.2305</v>
-      </c>
-      <c r="P13" t="n">
-        <v>-1.000300000000001</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>-33.0097</v>
-      </c>
-      <c r="R13" t="n">
-        <v>32.0091</v>
-      </c>
-      <c r="S13" t="n">
-        <v>9.069599999999998</v>
-      </c>
-      <c r="T13" t="n">
-        <v>4.393000000000001</v>
-      </c>
-      <c r="U13" t="n">
-        <v>4.6766</v>
-      </c>
-      <c r="V13" t="n">
-        <v>2.380700000000001</v>
-      </c>
-      <c r="W13" t="n">
-        <v>19.3335</v>
-      </c>
-      <c r="X13" t="n">
-        <v>-16.9527</v>
+      <c r="C14" t="n">
+        <v>6</v>
+      </c>
+      <c r="D14" t="n">
+        <v>-13.3595</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2.2274</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-15.5873</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-16.9292</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.0781</v>
+      </c>
+      <c r="I14" t="n">
+        <v>-18.0072</v>
+      </c>
+      <c r="J14" t="n">
+        <v>44.4132</v>
+      </c>
+      <c r="K14" t="n">
+        <v>36.226</v>
+      </c>
+      <c r="L14" t="n">
+        <v>8.186699999999998</v>
+      </c>
+      <c r="M14" t="n">
+        <v>-61.34239999999999</v>
+      </c>
+      <c r="N14" t="n">
+        <v>-35.148</v>
+      </c>
+      <c r="O14" t="n">
+        <v>-26.1942</v>
+      </c>
+      <c r="P14" t="n">
+        <v>9.736600000000003</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>-96.39449999999999</v>
+      </c>
+      <c r="R14" t="n">
+        <v>106.1308</v>
+      </c>
+      <c r="S14" t="n">
+        <v>12.5012</v>
+      </c>
+      <c r="T14" t="n">
+        <v>15.234</v>
+      </c>
+      <c r="U14" t="n">
+        <v>-2.7327</v>
+      </c>
+      <c r="V14" t="n">
+        <v>-18.6685</v>
+      </c>
+      <c r="W14" t="n">
+        <v>38.9761</v>
+      </c>
+      <c r="X14" t="n">
+        <v>-57.64409999999999</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_RIGALLI-ALGINET.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_RIGALLI-ALGINET.xlsx
@@ -565,13 +565,13 @@
         <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>11.9012</v>
+        <v>9.043699999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>11.5795</v>
+        <v>8.774900000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3217000000000001</v>
+        <v>0.2690000000000001</v>
       </c>
       <c r="G2" t="n">
         <v>6.2685</v>
@@ -610,13 +610,13 @@
         <v>9.152699999999999</v>
       </c>
       <c r="S2" t="n">
-        <v>5.4645</v>
+        <v>2.6071</v>
       </c>
       <c r="T2" t="n">
-        <v>4.6157</v>
+        <v>1.8109</v>
       </c>
       <c r="U2" t="n">
-        <v>0.8487999999999998</v>
+        <v>0.7961</v>
       </c>
       <c r="V2" t="n">
         <v>-4.700299999999999</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. MARTIN FERNANDEZ</t>
+          <t>M. MARTINEZ HERNANDEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>6.9258</v>
+        <v>4.978800000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>16.0741</v>
+        <v>0.3992000000000004</v>
       </c>
       <c r="F3" t="n">
-        <v>-9.148399999999999</v>
+        <v>4.5797</v>
       </c>
       <c r="G3" t="n">
-        <v>6.7826</v>
+        <v>-0.3994999999999997</v>
       </c>
       <c r="H3" t="n">
-        <v>6.5372</v>
+        <v>0.3553999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2454999999999999</v>
+        <v>-0.7549000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>11.5518</v>
+        <v>4.3575</v>
       </c>
       <c r="K3" t="n">
-        <v>9.2013</v>
+        <v>3.3078</v>
       </c>
       <c r="L3" t="n">
-        <v>2.3505</v>
+        <v>1.0498</v>
       </c>
       <c r="M3" t="n">
-        <v>-4.7692</v>
+        <v>-4.7569</v>
       </c>
       <c r="N3" t="n">
-        <v>-2.6642</v>
+        <v>-2.9522</v>
       </c>
       <c r="O3" t="n">
-        <v>-2.105</v>
+        <v>-1.8048</v>
       </c>
       <c r="P3" t="n">
-        <v>1.9472</v>
+        <v>3.7</v>
       </c>
       <c r="Q3" t="n">
-        <v>-5.8421</v>
+        <v>-9.1526</v>
       </c>
       <c r="R3" t="n">
-        <v>7.789400000000001</v>
+        <v>12.8525</v>
       </c>
       <c r="S3" t="n">
-        <v>9.6928</v>
+        <v>0.3790999999999999</v>
       </c>
       <c r="T3" t="n">
-        <v>9.9603</v>
+        <v>0.03049999999999999</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2675000000000001</v>
+        <v>0.3485</v>
       </c>
       <c r="V3" t="n">
-        <v>-11.4969</v>
+        <v>1.2992</v>
       </c>
       <c r="W3" t="n">
-        <v>0.4042000000000001</v>
+        <v>5.1638</v>
       </c>
       <c r="X3" t="n">
-        <v>-11.9009</v>
+        <v>-3.8644</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>1.279299999999999</v>
+        <v>3.2196</v>
       </c>
       <c r="E4" t="n">
-        <v>4.3268</v>
+        <v>5.5467</v>
       </c>
       <c r="F4" t="n">
-        <v>-3.0473</v>
+        <v>-2.3271</v>
       </c>
       <c r="G4" t="n">
         <v>-8.1607</v>
@@ -766,13 +766,13 @@
         <v>13.242</v>
       </c>
       <c r="S4" t="n">
-        <v>1.6439</v>
+        <v>3.5841</v>
       </c>
       <c r="T4" t="n">
-        <v>1.4538</v>
+        <v>2.6738</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1903</v>
+        <v>0.9105000000000001</v>
       </c>
       <c r="V4" t="n">
         <v>-1.1618</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. MARTINEZ HERNANDEZ</t>
+          <t>J. MARTIN FERNANDEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7976999999999994</v>
+        <v>1.6231</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.4775</v>
+        <v>10.317</v>
       </c>
       <c r="F5" t="n">
-        <v>3.2752</v>
+        <v>-8.694099999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.3994999999999997</v>
+        <v>6.7826</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3553999999999999</v>
+        <v>6.5372</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.7549000000000001</v>
+        <v>0.2454999999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>4.3575</v>
+        <v>11.5518</v>
       </c>
       <c r="K5" t="n">
-        <v>3.3078</v>
+        <v>9.2013</v>
       </c>
       <c r="L5" t="n">
-        <v>1.0498</v>
+        <v>2.3505</v>
       </c>
       <c r="M5" t="n">
-        <v>-4.7569</v>
+        <v>-4.7692</v>
       </c>
       <c r="N5" t="n">
-        <v>-2.9522</v>
+        <v>-2.6642</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.8048</v>
+        <v>-2.105</v>
       </c>
       <c r="P5" t="n">
-        <v>3.7</v>
+        <v>1.9472</v>
       </c>
       <c r="Q5" t="n">
-        <v>-9.1526</v>
+        <v>-5.8421</v>
       </c>
       <c r="R5" t="n">
-        <v>12.8525</v>
+        <v>7.789400000000001</v>
       </c>
       <c r="S5" t="n">
-        <v>-3.8021</v>
+        <v>4.3899</v>
       </c>
       <c r="T5" t="n">
-        <v>-2.8461</v>
+        <v>4.2031</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.9559</v>
+        <v>0.187</v>
       </c>
       <c r="V5" t="n">
-        <v>1.2992</v>
+        <v>-11.4969</v>
       </c>
       <c r="W5" t="n">
-        <v>5.1638</v>
+        <v>0.4042000000000001</v>
       </c>
       <c r="X5" t="n">
-        <v>-3.8644</v>
+        <v>-11.9009</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. CHOJNACKI</t>
+          <t>M. RODILLA ALCAIDE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,70 +874,70 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.2005000000000001</v>
+        <v>1.2846</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8925999999999999</v>
+        <v>2.2632</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.0932</v>
+        <v>-0.9785000000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.256</v>
+        <v>-1.1252</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1427</v>
+        <v>-0.7063</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3987</v>
+        <v>-0.419</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0334</v>
+        <v>5.8363</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6979</v>
+        <v>4.0106</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.6645</v>
+        <v>1.8256</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.2895</v>
+        <v>-6.9615</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.5553</v>
+        <v>-4.7168</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2658</v>
+        <v>-2.2445</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.1948</v>
+        <v>-0.7789999999999999</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9737</v>
+        <v>-11.0999</v>
       </c>
       <c r="R6" t="n">
-        <v>0.7789</v>
+        <v>10.321</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2503</v>
+        <v>0.6450999999999999</v>
       </c>
       <c r="T6" t="n">
-        <v>0.6118999999999999</v>
+        <v>1.5248</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3616</v>
+        <v>-0.8795999999999999</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>2.5436</v>
       </c>
       <c r="W6" t="n">
-        <v>1.2211</v>
+        <v>6.0021</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.2211</v>
+        <v>-3.4585</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>-3.418099999999999</v>
+        <v>0.7795000000000005</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.8152</v>
+        <v>0.1613999999999998</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.6031000000000001</v>
+        <v>0.618</v>
       </c>
       <c r="G7" t="n">
         <v>1.043099999999999</v>
@@ -1000,13 +1000,13 @@
         <v>10.3209</v>
       </c>
       <c r="S7" t="n">
-        <v>-5.1868</v>
+        <v>-0.9893999999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>-3.866</v>
+        <v>-0.8896000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.3208</v>
+        <v>-0.09979999999999989</v>
       </c>
       <c r="V7" t="n">
         <v>5.399299999999999</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. RODILLA ALCAIDE</t>
+          <t>M. CHOJNACKI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.5486</v>
+        <v>-0.2445000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.748</v>
+        <v>0.7929999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.8008</v>
+        <v>-1.0376</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.1252</v>
+        <v>-0.256</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.7063</v>
+        <v>0.1427</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.419</v>
+        <v>-0.3987</v>
       </c>
       <c r="J8" t="n">
-        <v>5.8363</v>
+        <v>0.0334</v>
       </c>
       <c r="K8" t="n">
-        <v>4.0106</v>
+        <v>0.6979</v>
       </c>
       <c r="L8" t="n">
-        <v>1.8256</v>
+        <v>-0.6645</v>
       </c>
       <c r="M8" t="n">
-        <v>-6.9615</v>
+        <v>-0.2895</v>
       </c>
       <c r="N8" t="n">
-        <v>-4.7168</v>
+        <v>-0.5553</v>
       </c>
       <c r="O8" t="n">
-        <v>-2.2445</v>
+        <v>0.2658</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.7789999999999999</v>
+        <v>-0.1948</v>
       </c>
       <c r="Q8" t="n">
-        <v>-11.0999</v>
+        <v>-0.9737</v>
       </c>
       <c r="R8" t="n">
-        <v>10.321</v>
+        <v>0.7789</v>
       </c>
       <c r="S8" t="n">
-        <v>-4.1882</v>
+        <v>0.2062</v>
       </c>
       <c r="T8" t="n">
-        <v>-2.4864</v>
+        <v>0.5122</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.7019</v>
+        <v>-0.306</v>
       </c>
       <c r="V8" t="n">
-        <v>2.5436</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>6.0021</v>
+        <v>1.2211</v>
       </c>
       <c r="X8" t="n">
-        <v>-3.4585</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>V. PELUFO LOZANO</t>
+          <t>A. ZURBRIGGEN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.4133</v>
+        <v>-3.674399999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>2.369</v>
+        <v>-13.9364</v>
       </c>
       <c r="F9" t="n">
-        <v>-6.782399999999999</v>
+        <v>10.2621</v>
       </c>
       <c r="G9" t="n">
-        <v>2.3954</v>
+        <v>-9.3126</v>
       </c>
       <c r="H9" t="n">
-        <v>4.379300000000001</v>
+        <v>-6.2238</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.984</v>
+        <v>-3.0888</v>
       </c>
       <c r="J9" t="n">
-        <v>10.4986</v>
+        <v>-7.4846</v>
       </c>
       <c r="K9" t="n">
-        <v>8.431699999999999</v>
+        <v>-3.7426</v>
       </c>
       <c r="L9" t="n">
-        <v>2.0668</v>
+        <v>-3.742</v>
       </c>
       <c r="M9" t="n">
-        <v>-8.103299999999999</v>
+        <v>-1.828</v>
       </c>
       <c r="N9" t="n">
-        <v>-4.0523</v>
+        <v>-2.4812</v>
       </c>
       <c r="O9" t="n">
-        <v>-4.0509</v>
+        <v>0.6531</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.7527</v>
+        <v>0.3894999999999998</v>
       </c>
       <c r="Q9" t="n">
-        <v>-12.8527</v>
+        <v>-12.0737</v>
       </c>
       <c r="R9" t="n">
-        <v>11.0999</v>
+        <v>12.4631</v>
       </c>
       <c r="S9" t="n">
-        <v>2.8808</v>
+        <v>0.4366999999999999</v>
       </c>
       <c r="T9" t="n">
-        <v>3.4288</v>
+        <v>-0.8360000000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5480000000000002</v>
+        <v>1.2728</v>
       </c>
       <c r="V9" t="n">
-        <v>-7.9367</v>
+        <v>4.812</v>
       </c>
       <c r="W9" t="n">
-        <v>1.2943</v>
+        <v>6.458</v>
       </c>
       <c r="X9" t="n">
-        <v>-9.231</v>
+        <v>-1.6459</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. ZURBRIGGEN</t>
+          <t>R. MALLIK BOUNAD</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.5094</v>
+        <v>-4.9759</v>
       </c>
       <c r="E10" t="n">
-        <v>-15.4795</v>
+        <v>-5.0352</v>
       </c>
       <c r="F10" t="n">
-        <v>10.9701</v>
+        <v>0.05929999999999991</v>
       </c>
       <c r="G10" t="n">
-        <v>-9.3126</v>
+        <v>-3.9631</v>
       </c>
       <c r="H10" t="n">
-        <v>-6.2238</v>
+        <v>1.4281</v>
       </c>
       <c r="I10" t="n">
-        <v>-3.0888</v>
+        <v>-5.3912</v>
       </c>
       <c r="J10" t="n">
-        <v>-7.4846</v>
+        <v>3.8469</v>
       </c>
       <c r="K10" t="n">
-        <v>-3.7426</v>
+        <v>5.239599999999999</v>
       </c>
       <c r="L10" t="n">
-        <v>-3.742</v>
+        <v>-1.3926</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.828</v>
+        <v>-7.8101</v>
       </c>
       <c r="N10" t="n">
-        <v>-2.4812</v>
+        <v>-3.8115</v>
       </c>
       <c r="O10" t="n">
-        <v>0.6531</v>
+        <v>-3.9985</v>
       </c>
       <c r="P10" t="n">
-        <v>0.3894999999999998</v>
+        <v>-2.142</v>
       </c>
       <c r="Q10" t="n">
-        <v>-12.0737</v>
+        <v>-12.6578</v>
       </c>
       <c r="R10" t="n">
-        <v>12.4631</v>
+        <v>10.5158</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3983</v>
+        <v>1.7886</v>
       </c>
       <c r="T10" t="n">
-        <v>-2.3793</v>
+        <v>2.9155</v>
       </c>
       <c r="U10" t="n">
-        <v>1.9809</v>
+        <v>-1.1269</v>
       </c>
       <c r="V10" t="n">
-        <v>4.812</v>
+        <v>-0.6595</v>
       </c>
       <c r="W10" t="n">
-        <v>6.458</v>
+        <v>0.8601000000000001</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.6459</v>
+        <v>-1.5196</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. BOSCH ROIG</t>
+          <t>H. MARTORELL TRONCHONI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.1172</v>
+        <v>-6.0517</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.1639000000000002</v>
+        <v>-4.673100000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>-4.953200000000001</v>
+        <v>-1.3787</v>
       </c>
       <c r="G11" t="n">
-        <v>-6.2799</v>
+        <v>-3.9218</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.2695</v>
+        <v>-3.0932</v>
       </c>
       <c r="I11" t="n">
-        <v>-5.0104</v>
+        <v>-0.8284</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.3396</v>
+        <v>-1.8256</v>
       </c>
       <c r="K11" t="n">
-        <v>0.8880000000000001</v>
+        <v>-1.2828</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.2277</v>
+        <v>-0.5428999999999999</v>
       </c>
       <c r="M11" t="n">
-        <v>-4.940300000000001</v>
+        <v>-2.096</v>
       </c>
       <c r="N11" t="n">
-        <v>-2.1576</v>
+        <v>-1.8106</v>
       </c>
       <c r="O11" t="n">
-        <v>-2.7827</v>
+        <v>-0.2856</v>
       </c>
       <c r="P11" t="n">
-        <v>1.9474</v>
+        <v>-2.5316</v>
       </c>
       <c r="Q11" t="n">
-        <v>-4.2842</v>
+        <v>-3.8947</v>
       </c>
       <c r="R11" t="n">
-        <v>6.2315</v>
+        <v>1.3631</v>
       </c>
       <c r="S11" t="n">
-        <v>6.2622</v>
+        <v>0.1221</v>
       </c>
       <c r="T11" t="n">
-        <v>3.6799</v>
+        <v>0.7678</v>
       </c>
       <c r="U11" t="n">
-        <v>2.5825</v>
+        <v>-0.6458</v>
       </c>
       <c r="V11" t="n">
-        <v>-7.0469</v>
+        <v>0.2795</v>
       </c>
       <c r="W11" t="n">
-        <v>1.78</v>
+        <v>0.2795</v>
       </c>
       <c r="X11" t="n">
-        <v>-8.827</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>H. MARTORELL TRONCHONI</t>
+          <t>V. PELUFO LOZANO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.501600000000001</v>
+        <v>-6.2927</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.8725</v>
+        <v>0.9597</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.6291</v>
+        <v>-7.2524</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.9218</v>
+        <v>2.3954</v>
       </c>
       <c r="H12" t="n">
-        <v>-3.0932</v>
+        <v>4.379300000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.8284</v>
+        <v>-1.984</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.8256</v>
+        <v>10.4986</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.2828</v>
+        <v>8.431699999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.5428999999999999</v>
+        <v>2.0668</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.096</v>
+        <v>-8.103299999999999</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.8106</v>
+        <v>-4.0523</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.2856</v>
+        <v>-4.0509</v>
       </c>
       <c r="P12" t="n">
-        <v>-2.5316</v>
+        <v>-1.7527</v>
       </c>
       <c r="Q12" t="n">
-        <v>-3.8947</v>
+        <v>-12.8527</v>
       </c>
       <c r="R12" t="n">
-        <v>1.3631</v>
+        <v>11.0999</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3276</v>
+        <v>1.0014</v>
       </c>
       <c r="T12" t="n">
-        <v>0.5685</v>
+        <v>2.0194</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.8964</v>
+        <v>-1.0181</v>
       </c>
       <c r="V12" t="n">
-        <v>0.2795</v>
+        <v>-7.9367</v>
       </c>
       <c r="W12" t="n">
-        <v>0.2795</v>
+        <v>1.2943</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-9.231</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>R. MALLIK BOUNAD</t>
+          <t>J. BOSCH ROIG</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.5548</v>
+        <v>-6.8056</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.458</v>
+        <v>-1.7967</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.0968</v>
+        <v>-5.009</v>
       </c>
       <c r="G13" t="n">
-        <v>-3.9631</v>
+        <v>-6.2799</v>
       </c>
       <c r="H13" t="n">
-        <v>1.4281</v>
+        <v>-1.2695</v>
       </c>
       <c r="I13" t="n">
-        <v>-5.3912</v>
+        <v>-5.0104</v>
       </c>
       <c r="J13" t="n">
-        <v>3.8469</v>
+        <v>-1.3396</v>
       </c>
       <c r="K13" t="n">
-        <v>5.239599999999999</v>
+        <v>0.8880000000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.3926</v>
+        <v>-2.2277</v>
       </c>
       <c r="M13" t="n">
-        <v>-7.8101</v>
+        <v>-4.940300000000001</v>
       </c>
       <c r="N13" t="n">
-        <v>-3.8115</v>
+        <v>-2.1576</v>
       </c>
       <c r="O13" t="n">
-        <v>-3.9985</v>
+        <v>-2.7827</v>
       </c>
       <c r="P13" t="n">
-        <v>-2.142</v>
+        <v>1.9474</v>
       </c>
       <c r="Q13" t="n">
-        <v>-12.6578</v>
+        <v>-4.2842</v>
       </c>
       <c r="R13" t="n">
-        <v>10.5158</v>
+        <v>6.2315</v>
       </c>
       <c r="S13" t="n">
-        <v>0.2097</v>
+        <v>4.5737</v>
       </c>
       <c r="T13" t="n">
-        <v>2.4929</v>
+        <v>2.0471</v>
       </c>
       <c r="U13" t="n">
-        <v>-2.2831</v>
+        <v>2.5267</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.6595</v>
+        <v>-7.0469</v>
       </c>
       <c r="W13" t="n">
-        <v>0.8601000000000001</v>
+        <v>1.78</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.5196</v>
+        <v>-8.827</v>
       </c>
     </row>
     <row r="14">
@@ -1501,19 +1501,19 @@
         <v>6</v>
       </c>
       <c r="D14" t="n">
-        <v>-13.3595</v>
+        <v>-7.115499999999995</v>
       </c>
       <c r="E14" t="n">
-        <v>2.2274</v>
+        <v>3.773700000000002</v>
       </c>
       <c r="F14" t="n">
-        <v>-15.5873</v>
+        <v>-10.8893</v>
       </c>
       <c r="G14" t="n">
         <v>-16.9292</v>
       </c>
       <c r="H14" t="n">
-        <v>1.0781</v>
+        <v>1.078099999999999</v>
       </c>
       <c r="I14" t="n">
         <v>-18.0072</v>
@@ -1525,10 +1525,10 @@
         <v>36.226</v>
       </c>
       <c r="L14" t="n">
-        <v>8.186699999999998</v>
+        <v>8.1867</v>
       </c>
       <c r="M14" t="n">
-        <v>-61.34239999999999</v>
+        <v>-61.3424</v>
       </c>
       <c r="N14" t="n">
         <v>-35.148</v>
@@ -1546,19 +1546,19 @@
         <v>106.1308</v>
       </c>
       <c r="S14" t="n">
-        <v>12.5012</v>
+        <v>18.7446</v>
       </c>
       <c r="T14" t="n">
-        <v>15.234</v>
+        <v>16.7795</v>
       </c>
       <c r="U14" t="n">
-        <v>-2.7327</v>
+        <v>1.9654</v>
       </c>
       <c r="V14" t="n">
         <v>-18.6685</v>
       </c>
       <c r="W14" t="n">
-        <v>38.9761</v>
+        <v>38.97610000000001</v>
       </c>
       <c r="X14" t="n">
         <v>-57.64409999999999</v>
